--- a/data/2026/35-suceava/146263-suceava/budget_file.xlsx
+++ b/data/2026/35-suceava/146263-suceava/budget_file.xlsx
@@ -841,64 +841,76 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>07.02.01</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>A3. IMPOZITE SI TAXE PE PROPRIETATE</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>87651550</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
+      <c r="G13" s="5" t="n">
+        <v>108423930</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>07.02.01 total: parent 108.423.930,00 != sum(children) 87.651.550,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>07.02</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Impozite si taxe pe proprietate</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="5" t="n">
         <v>108423930</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>07.02 total: parent 108.423.930,00 != sum(children) 129.196.310,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -7306,33 +7318,39 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="B160" s="4" t="n"/>
+      <c r="C160" s="4" t="inlineStr">
         <is>
           <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F160" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G160" s="3" t="n">
+      <c r="G160" s="5" t="n">
         <v>37001100</v>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>51.02 total: parent 37.001.100,00 != sum(children) 1.210.790,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -9061,33 +9079,39 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="4" t="inlineStr">
         <is>
           <t>54.02</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="4" t="inlineStr">
         <is>
           <t>Alte servicii publice generale</t>
         </is>
       </c>
-      <c r="D209" t="n">
+      <c r="D209" s="4" t="n">
         <v>265</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F209" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G209" s="3" t="n">
+      <c r="G209" s="5" t="n">
         <v>21464230</v>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>54.02 total: parent 21.464.230,00 != sum(children) 17.850,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -10684,33 +10708,39 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="4" t="inlineStr">
         <is>
           <t>61.02</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="B255" s="4" t="n"/>
+      <c r="C255" s="4" t="inlineStr">
         <is>
           <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
-      <c r="D255" t="n">
+      <c r="D255" s="4" t="n">
         <v>311</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F255" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G255" s="3" t="n">
+      <c r="G255" s="5" t="n">
         <v>16148960</v>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr">
+        <is>
+          <t>61.02 total: parent 16.148.960,00 != sum(children) 1.607.270,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -12460,33 +12490,39 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
+      <c r="A305" s="4" t="inlineStr">
         <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
+      <c r="B305" s="4" t="n"/>
+      <c r="C305" s="4" t="inlineStr">
         <is>
           <t>Invatamant</t>
         </is>
       </c>
-      <c r="D305" t="n">
+      <c r="D305" s="4" t="n">
         <v>361</v>
       </c>
-      <c r="E305" t="n">
+      <c r="E305" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F305" t="inlineStr">
+      <c r="F305" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G305" s="3" t="n">
+      <c r="G305" s="5" t="n">
         <v>162716630</v>
       </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H305" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I305" s="4" t="inlineStr">
+        <is>
+          <t>65.02 total: parent 162.716.630,00 != sum(children) 1.897.110,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -15132,33 +15168,39 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
+      <c r="A381" s="4" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
+      <c r="B381" s="4" t="n"/>
+      <c r="C381" s="4" t="inlineStr">
         <is>
           <t>Sanatate</t>
         </is>
       </c>
-      <c r="D381" t="n">
+      <c r="D381" s="4" t="n">
         <v>437</v>
       </c>
-      <c r="E381" t="n">
+      <c r="E381" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F381" t="inlineStr">
+      <c r="F381" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G381" s="3" t="n">
+      <c r="G381" s="5" t="n">
         <v>8521400</v>
       </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H381" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I381" s="4" t="inlineStr">
+        <is>
+          <t>66.02 total: parent 8.521.400,00 != sum(children) 50.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -16157,33 +16199,39 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
+      <c r="A410" s="4" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
+      <c r="B410" s="4" t="n"/>
+      <c r="C410" s="4" t="inlineStr">
         <is>
           <t>Cultura, recreere si religie</t>
         </is>
       </c>
-      <c r="D410" t="n">
+      <c r="D410" s="4" t="n">
         <v>466</v>
       </c>
-      <c r="E410" t="n">
+      <c r="E410" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="F410" t="inlineStr">
+      <c r="F410" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G410" s="3" t="n">
+      <c r="G410" s="5" t="n">
         <v>106184010</v>
       </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H410" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I410" s="4" t="inlineStr">
+        <is>
+          <t>67.02 total: parent 106.184.010,00 != sum(children) 6.005.050,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -18880,33 +18928,39 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
+      <c r="A487" s="4" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr">
+      <c r="B487" s="4" t="n"/>
+      <c r="C487" s="4" t="inlineStr">
         <is>
           <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
-      <c r="D487" t="n">
+      <c r="D487" s="4" t="n">
         <v>543</v>
       </c>
-      <c r="E487" t="n">
+      <c r="E487" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F487" t="inlineStr">
+      <c r="F487" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G487" s="3" t="n">
+      <c r="G487" s="5" t="n">
         <v>50847240</v>
       </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H487" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I487" s="4" t="inlineStr">
+        <is>
+          <t>68.02 total: parent 50.847.240,00 != sum(children) 40.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20796,33 +20850,39 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
+      <c r="A542" s="4" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
+      <c r="B542" s="4" t="n"/>
+      <c r="C542" s="4" t="inlineStr">
         <is>
           <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
-      <c r="D542" t="n">
+      <c r="D542" s="4" t="n">
         <v>598</v>
       </c>
-      <c r="E542" t="n">
+      <c r="E542" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="F542" t="inlineStr">
+      <c r="F542" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G542" s="3" t="n">
+      <c r="G542" s="5" t="n">
         <v>77707510</v>
       </c>
-      <c r="H542" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H542" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I542" s="4" t="inlineStr">
+        <is>
+          <t>70.02 total: parent 77.707.510,00 != sum(children) 19.964.420,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -22444,33 +22504,39 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
+      <c r="A589" s="4" t="inlineStr">
         <is>
           <t>74.02</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="B589" s="4" t="n"/>
+      <c r="C589" s="4" t="inlineStr">
         <is>
           <t>Protectia mediului</t>
         </is>
       </c>
-      <c r="D589" t="n">
+      <c r="D589" s="4" t="n">
         <v>645</v>
       </c>
-      <c r="E589" t="n">
+      <c r="E589" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F589" t="inlineStr">
+      <c r="F589" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G589" s="3" t="n">
+      <c r="G589" s="5" t="n">
         <v>72851870</v>
       </c>
-      <c r="H589" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H589" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I589" s="4" t="inlineStr">
+        <is>
+          <t>74.02 total: parent 72.851.870,00 != sum(children) 3.555.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -24364,33 +24430,39 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr">
+      <c r="A643" s="4" t="inlineStr">
         <is>
           <t>80.02</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="B643" s="4" t="n"/>
+      <c r="C643" s="4" t="inlineStr">
         <is>
           <t>Actiuni generale economice, comerciale si de munca</t>
         </is>
       </c>
-      <c r="D643" t="n">
+      <c r="D643" s="4" t="n">
         <v>699</v>
       </c>
-      <c r="E643" t="n">
+      <c r="E643" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="F643" t="inlineStr">
+      <c r="F643" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G643" s="3" t="n">
+      <c r="G643" s="5" t="n">
         <v>531440</v>
       </c>
-      <c r="H643" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H643" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I643" s="4" t="inlineStr">
+        <is>
+          <t>80.02 total: parent 531.440,00 != sum(children) 33.700,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -24823,33 +24895,39 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr">
+      <c r="A656" s="4" t="inlineStr">
         <is>
           <t>81.02</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="B656" s="4" t="n"/>
+      <c r="C656" s="4" t="inlineStr">
         <is>
           <t>Combustibili si energie</t>
         </is>
       </c>
-      <c r="D656" t="n">
+      <c r="D656" s="4" t="n">
         <v>712</v>
       </c>
-      <c r="E656" t="n">
+      <c r="E656" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="F656" t="inlineStr">
+      <c r="F656" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G656" s="3" t="n">
+      <c r="G656" s="5" t="n">
         <v>10809200</v>
       </c>
-      <c r="H656" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H656" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I656" s="4" t="inlineStr">
+        <is>
+          <t>81.02 total: parent 10.809.200,00 != sum(children) 6.121.140,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -25493,33 +25571,39 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
+      <c r="A675" s="4" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="B675" s="4" t="n"/>
+      <c r="C675" s="4" t="inlineStr">
         <is>
           <t>Transporturi</t>
         </is>
       </c>
-      <c r="D675" t="n">
+      <c r="D675" s="4" t="n">
         <v>731</v>
       </c>
-      <c r="E675" t="n">
+      <c r="E675" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="F675" t="inlineStr">
+      <c r="F675" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G675" s="3" t="n">
+      <c r="G675" s="5" t="n">
         <v>185675880</v>
       </c>
-      <c r="H675" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H675" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I675" s="4" t="inlineStr">
+        <is>
+          <t>84.02 total: parent 185.675.880,00 != sum(children) 23.454.580,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -27277,7 +27361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27323,12 +27407,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27336,29 +27420,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>07.02.01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 07.02.01 total: sum now consistent — applied</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27366,7 +27445,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>07.02.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -27376,27 +27455,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 total: sum now consistent — applied</t>
+          <t>07.02.01 total: parent 108.423.930,00 != sum(children) 87.651.550,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>07.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -27406,14 +27485,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>07.02 total: parent 108.423.930,00 != sum(children) 129.196.310,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -27422,28 +27501,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>07.02.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -27452,41 +27526,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 39.02 total: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -27496,87 +27565,77 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>11.02 total: parent 106.278.000,00 != sum(children) 246.152.870,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 54.02 total: sum now consistent — applied</t>
+          <t>code 30.00.02 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -27586,57 +27645,52 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 61.02 total: sum now consistent — applied</t>
+          <t>30.02 total: parent 10.775.000,00 != sum(children) 68.506.970,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 total: sum now consistent — applied</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -27646,57 +27700,52 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 66.02 total: sum now consistent — applied</t>
+          <t>39.02 total: parent 217.000,00 != sum(children) 434.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 67.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -27706,87 +27755,77 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 68.02 total: sum now consistent — applied</t>
+          <t>42.02 total: parent 100.291.270,00 != sum(children) 205.510.280,00 (8 children)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 70.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (17%): 'TIL           A PNRR' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 74.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (11%): 'TIM            R' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -27796,74 +27835,64 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 total: sum now consistent — applied</t>
+          <t>51.02 total: parent 37.001.100,00 != sum(children) 1.210.790,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>81.02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 81.02 total: sum now consistent — applied</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (18%): 'cher  o   a  e   e   le' vs 'Cheltuieli judiciare si extrajudiciare d'</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -27872,16 +27901,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>54.02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>54.02 total: parent 21.464.230,00 != sum(children) 17.850,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -27897,23 +27931,23 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>07.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -27922,16 +27956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -27947,11 +27981,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -27961,14 +27995,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11.02 total: parent 106.278.000,00 != sum(children) 246.152.870,00 (4 children)</t>
+          <t>61.02 total: parent 16.148.960,00 != sum(children) 1.607.270,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -27977,23 +28011,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -28002,53 +28036,53 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30.00.02</t>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>code 30.00.02 (revenue) not in nomenclator</t>
+          <t>65.02 total: parent 162.716.630,00 != sum(children) 1.897.110,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30.02 total: parent 10.775.000,00 != sum(children) 68.506.970,00 (3 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -28057,101 +28091,101 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>66.02 total: parent 8.521.400,00 != sum(children) 50.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39.02 total: parent 217.000,00 != sum(children) 434.000,00 (2 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>67.02 total: parent 106.184.010,00 != sum(children) 6.005.050,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42.02 total: parent 100.291.270,00 != sum(children) 205.510.280,00 (8 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -28167,41 +28201,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (17%): 'TIL           A PNRR' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
+          <t>name mismatch vs nomenclator (17%): 'TIE  E      E  RE' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (11%): 'TIM            R' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
+          <t>68.02 total: parent 50.847.240,00 != sum(children) 40.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -28217,7 +28256,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -28233,25 +28272,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'cher  o   a  e   e   le' vs 'Cheltuieli judiciare si extrajudiciare d'</t>
+          <t>70.02 total: parent 77.707.510,00 != sum(children) 19.964.420,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -28267,7 +28311,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -28283,25 +28327,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>74.02 total: parent 72.851.870,00 != sum(children) 3.555.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -28317,7 +28366,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -28333,7 +28382,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -28342,23 +28391,23 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (23%): 'Ssu   ud  z te' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -28367,23 +28416,23 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (18%): 'TIL           TA PNRR' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -28392,41 +28441,46 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (13%): 'TIM          E  R' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>80.02</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (17%): 'TIE  E      E  RE' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
+          <t>80.02 total: parent 531.440,00 != sum(children) 33.700,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -28442,7 +28496,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -28458,7 +28512,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -28467,48 +28521,53 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (17%): 'TIE  E      E  RE' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>81.02</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>81.02 total: parent 10.809.200,00 != sum(children) 6.121.140,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -28517,48 +28576,53 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>55.01.84</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'Ssu   ud  z te' vs 'Sume reprezentând stimulentul pentru cas'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'TIL           TA PNRR' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
+          <t>84.02 total: parent 185.675.880,00 != sum(children) 23.454.580,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -28567,16 +28631,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (13%): 'TIM          E  R' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -28586,120 +28650,20 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>01</t>
+        <v>29</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>26</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (17%): 'TIE  E      E  RE' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>27</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>27</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>29</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
         <is>
           <t>unparseable cell '84.02.03.02 112.472.000' in column total</t>
         </is>
@@ -28716,7 +28680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -28738,7 +28702,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -28748,72 +28712,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>775</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>743</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.90000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4a266d5e2a76355b46127fd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>f965a34a536602ccad08a33d81b91f238308f1690a906777f4fd6baf9503e67e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 1)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-29, 782 linii</t>
         </is>
